--- a/trades_log.xlsx
+++ b/trades_log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,129 +433,129 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>spread</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>leverage</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>base_capital</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>first_leg_price</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>second_leg_price</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>position_size_usd</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>first_leg_weight</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>second_leg_weight</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>first_leg_position_usd</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>second_leg_position_usd</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>equity_before</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>entry_commission</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>first_leg_pnl_%</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>second_leg_pnl_%</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>first_leg_pnl_usd</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>second_leg_pnl_usd</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>total_pnl_%</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pnl_usd</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>equity_after</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>exit_reason</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44214.75</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -603,7 +615,7 @@
       <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44226.70833333334</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -681,7 +693,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44226.70833333334</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -741,7 +753,7 @@
       <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44244.04166666666</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -819,7 +831,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44250.375</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -879,7 +891,7 @@
       <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44260.04166666666</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -957,7 +969,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44262.79166666666</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1017,7 +1029,7 @@
       <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44268.45833333334</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1095,7 +1107,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44278.66666666666</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1155,7 +1167,7 @@
       <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44296.45833333334</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1233,7 +1245,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44297.70833333334</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1293,7 +1305,7 @@
       <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44303.83333333334</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1371,7 +1383,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44307.58333333334</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1431,7 +1443,7 @@
       <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44311.54166666666</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1509,7 +1521,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44329.75</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1569,7 +1581,7 @@
       <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44332.08333333334</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1647,7 +1659,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44332.08333333334</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1707,7 +1719,7 @@
       <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44354.41666666666</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1797,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44355.41666666666</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1845,7 +1857,7 @@
       <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44359.25</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1923,7 +1935,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44371.625</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1983,7 +1995,7 @@
       <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44393.79166666666</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2061,7 +2073,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44411.45833333334</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2121,7 +2133,7 @@
       <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44418.41666666666</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2199,7 +2211,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44455.5</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -2259,7 +2271,7 @@
       <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44464.16666666666</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2337,7 +2349,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44464.16666666666</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2397,7 +2409,7 @@
       <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44467.41666666666</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2475,7 +2487,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44467.41666666666</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2535,7 +2547,7 @@
       <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44470.83333333334</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44471.70833333334</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2673,7 +2685,7 @@
       <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44482.54166666666</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2751,7 +2763,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44482.79166666666</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2811,7 +2823,7 @@
       <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44508.45833333334</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2889,7 +2901,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44508.5</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2949,7 +2961,7 @@
       <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44517.125</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -3027,7 +3039,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44524.45833333334</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -3087,7 +3099,7 @@
       <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44536</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -3165,7 +3177,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44542.20833333334</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -3225,7 +3237,7 @@
       <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44550.04166666666</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -3303,7 +3315,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44566.875</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -3363,7 +3375,7 @@
       <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44582.20833333334</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -3441,7 +3453,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44583.41666666666</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -3501,7 +3513,7 @@
       <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44589.83333333334</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -3579,7 +3591,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44589.83333333334</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -3639,7 +3651,7 @@
       <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44591.25</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -3717,7 +3729,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44591.25</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -3777,7 +3789,7 @@
       <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44593.79166666666</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3855,7 +3867,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44593.79166666666</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3915,7 +3927,7 @@
       <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44599.66666666666</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3993,7 +4005,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44621.45833333334</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -4053,7 +4065,7 @@
       <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44637.5</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -4131,7 +4143,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44693.95833333334</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -4191,7 +4203,7 @@
       <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44714.66666666666</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -4269,7 +4281,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44722.25</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -4329,7 +4341,7 @@
       <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44723.375</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -4407,7 +4419,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44723.375</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -4467,7 +4479,7 @@
       <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44731.04166666666</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -4545,7 +4557,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44731.83333333334</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -4605,7 +4617,7 @@
       <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44736.54166666666</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -4683,7 +4695,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44779.16666666666</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -4743,7 +4755,7 @@
       <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44791.20833333334</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -4821,7 +4833,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44792.91666666666</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -4881,7 +4893,7 @@
       <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44799.66666666666</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -4959,7 +4971,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44799.66666666666</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -5019,7 +5031,7 @@
       <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44814</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -5097,7 +5109,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44814</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -5157,7 +5169,7 @@
       <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44847.375</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -5235,7 +5247,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44847.375</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -5295,7 +5307,7 @@
       <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44856.375</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -5373,7 +5385,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44856.375</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -5433,7 +5445,7 @@
       <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44856.83333333334</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -5511,7 +5523,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44856.83333333334</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -5571,7 +5583,7 @@
       <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44870.04166666666</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -5649,7 +5661,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44878.58333333334</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -5709,7 +5721,7 @@
       <c r="X76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44882.16666666666</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -5787,7 +5799,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44882.83333333334</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -5847,7 +5859,7 @@
       <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44898.83333333334</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -5925,7 +5937,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44903.625</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -5985,7 +5997,7 @@
       <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44908.625</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -6063,7 +6075,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44919.25</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -6123,7 +6135,7 @@
       <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44925.54166666666</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -6201,7 +6213,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44938.25</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -6261,7 +6273,7 @@
       <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44953.33333333334</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -6339,7 +6351,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44955.29166666666</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -6399,7 +6411,7 @@
       <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44966.83333333334</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -6477,7 +6489,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44967.70833333334</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -6537,7 +6549,7 @@
       <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>44981.54166666666</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -6615,7 +6627,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44981.54166666666</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -6675,7 +6687,7 @@
       <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44985.625</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -6753,7 +6765,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44987.375</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -6813,7 +6825,7 @@
       <c r="X92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44995.20833333334</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -6891,7 +6903,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>44996.25</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -6951,7 +6963,7 @@
       <c r="X94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45009.70833333334</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -7029,7 +7041,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45028.16666666666</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -7089,7 +7101,7 @@
       <c r="X96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45034.91666666666</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -7167,7 +7179,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45044.41666666666</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -7227,7 +7239,7 @@
       <c r="X98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45051.875</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -7305,7 +7317,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45066.125</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -7365,7 +7377,7 @@
       <c r="X100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45068.125</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -7443,7 +7455,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45069.33333333334</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -7503,7 +7515,7 @@
       <c r="X102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45082.91666666666</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -7581,7 +7593,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45082.91666666666</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -7641,7 +7653,7 @@
       <c r="X104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45089.66666666666</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -7719,7 +7731,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45107.08333333334</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -7779,7 +7791,7 @@
       <c r="X106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45115.04166666666</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -7857,7 +7869,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45122.70833333334</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -7917,7 +7929,7 @@
       <c r="X108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45127.5</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -7995,7 +8007,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45129.20833333334</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -8055,7 +8067,7 @@
       <c r="X110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45139.25</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -8133,7 +8145,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45179.625</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -8193,7 +8205,7 @@
       <c r="X112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45187.45833333334</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -8271,7 +8283,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45205.20833333334</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -8331,7 +8343,7 @@
       <c r="X114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45212.33333333334</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -8409,7 +8421,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45212.33333333334</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -8469,7 +8481,7 @@
       <c r="X116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45230.95833333334</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -8547,7 +8559,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45231.04166666666</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -8607,7 +8619,7 @@
       <c r="X118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45252.41666666666</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -8685,7 +8697,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45252.41666666666</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -8745,7 +8757,7 @@
       <c r="X120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45260.66666666666</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -8823,7 +8835,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45260.66666666666</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -8883,7 +8895,7 @@
       <c r="X122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45262.33333333334</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -8961,7 +8973,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45262.33333333334</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -9021,7 +9033,7 @@
       <c r="X124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45271.75</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -9099,7 +9111,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45287.20833333334</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -9159,7 +9171,7 @@
       <c r="X126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45294.125</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -9237,7 +9249,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45301.125</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -9297,7 +9309,7 @@
       <c r="X128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45303.125</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -9375,7 +9387,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45310.70833333334</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -9435,7 +9447,7 @@
       <c r="X130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45329.125</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -9513,7 +9525,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45342.54166666666</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -9573,7 +9585,7 @@
       <c r="X132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45349.5</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -9651,7 +9663,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45366.25</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -9711,7 +9723,7 @@
       <c r="X134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45384.29166666666</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -9789,7 +9801,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45419.75</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -9849,7 +9861,7 @@
       <c r="X136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45423.625</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -9927,7 +9939,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45423.95833333334</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -9987,7 +9999,7 @@
       <c r="X138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45429.625</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -10065,7 +10077,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45450.83333333334</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -10125,7 +10137,7 @@
       <c r="X140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45462.33333333334</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -10203,7 +10215,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45475.375</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -10263,7 +10275,7 @@
       <c r="X142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45488.08333333334</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -10341,7 +10353,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45498.125</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -10401,7 +10413,7 @@
       <c r="X144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45505.95833333334</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -10479,7 +10491,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45506.45833333334</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -10539,7 +10551,7 @@
       <c r="X146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45540.16666666666</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -10617,7 +10629,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45547.20833333334</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -10677,7 +10689,7 @@
       <c r="X148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45553.41666666666</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -10755,7 +10767,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45560.25</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -10815,7 +10827,7 @@
       <c r="X150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45563.91666666666</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -10893,7 +10905,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45576.16666666666</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -10953,7 +10965,7 @@
       <c r="X152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45587.08333333334</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -11031,7 +11043,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45587.33333333334</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -11091,7 +11103,7 @@
       <c r="X154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45595.54166666666</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -11169,7 +11181,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45596.70833333334</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -11229,7 +11241,7 @@
       <c r="X156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45606.08333333334</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -11307,7 +11319,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45611.70833333334</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -11367,7 +11379,7 @@
       <c r="X158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45613.625</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -11445,7 +11457,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45613.625</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -11505,7 +11517,7 @@
       <c r="X160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45631.29166666666</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -11583,7 +11595,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45638.5</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -11643,7 +11655,7 @@
       <c r="X162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45642.16666666666</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -11721,7 +11733,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45643.54166666666</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -11781,7 +11793,7 @@
       <c r="X164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45668.5</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -11859,7 +11871,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45672.5</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -11919,7 +11931,7 @@
       <c r="X166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45673.91666666666</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -11997,7 +12009,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45673.91666666666</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -12057,7 +12069,7 @@
       <c r="X168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -12135,7 +12147,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45699.41666666666</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -12195,7 +12207,7 @@
       <c r="X170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45706.04166666666</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -12273,7 +12285,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45706.08333333334</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -12333,7 +12345,7 @@
       <c r="X172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45709.08333333334</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -12411,7 +12423,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45713.45833333334</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -12471,7 +12483,7 @@
       <c r="X174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45721.29166666666</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -12549,7 +12561,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45722.29166666666</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -12609,7 +12621,7 @@
       <c r="X176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45726.33333333334</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -12687,7 +12699,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45735.125</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -12747,7 +12759,7 @@
       <c r="X178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45754.125</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -12825,7 +12837,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45762.29166666666</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -12885,7 +12897,7 @@
       <c r="X180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45767.45833333334</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -12963,7 +12975,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45806.79166666666</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -13023,7 +13035,7 @@
       <c r="X182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45828.75</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -13101,7 +13113,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45848.41666666666</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -13161,7 +13173,7 @@
       <c r="X184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45849.5</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -13239,7 +13251,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45849.5</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -13299,7 +13311,7 @@
       <c r="X186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45855.75</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -13377,7 +13389,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45855.83333333334</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -13437,7 +13449,7 @@
       <c r="X188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45864.83333333334</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -13515,7 +13527,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45864.83333333334</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -13575,7 +13587,7 @@
       <c r="X190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45877.79166666666</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -13653,7 +13665,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45877.79166666666</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -13713,7 +13725,7 @@
       <c r="X192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45888.125</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -13791,7 +13803,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45888.125</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -13851,7 +13863,7 @@
       <c r="X194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45905.875</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -13929,7 +13941,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45918.5</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -13989,7 +14001,7 @@
       <c r="X196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45930.125</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -14067,7 +14079,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45940.91666666666</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -14127,7 +14139,7 @@
       <c r="X198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45950.16666666666</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -14205,7 +14217,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45950.58333333334</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -14265,7 +14277,7 @@
       <c r="X200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45961.75</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -14343,7 +14355,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45973.45833333334</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -14403,7 +14415,7 @@
       <c r="X202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45974.91666666666</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -14481,7 +14493,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45974.95833333334</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -14541,7 +14553,7 @@
       <c r="X204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45986.41666666666</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -14619,7 +14631,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45994.41666666666</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -14679,7 +14691,7 @@
       <c r="X206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45995.16666666666</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -14757,7 +14769,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45995.16666666666</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -14817,7 +14829,7 @@
       <c r="X208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>46017.5</v>
       </c>
       <c r="B209" t="inlineStr">
